--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484118_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484118_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2401</v>
+        <v>6.3687</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5026</v>
+        <v>3.4629</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7375</v>
+        <v>2.9059</v>
       </c>
       <c r="G2" t="n">
         <v>1.0072</v>
@@ -610,13 +610,13 @@
         <v>3.3725</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1145</v>
+        <v>0.0142</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1699</v>
+        <v>-0.2096</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0555</v>
+        <v>0.2238</v>
       </c>
       <c r="V2" t="n">
         <v>2.9668</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1357</v>
+        <v>3.1076</v>
       </c>
       <c r="E3" t="n">
         <v>1.5736</v>
       </c>
       <c r="F3" t="n">
-        <v>1.562</v>
+        <v>1.534</v>
       </c>
       <c r="G3" t="n">
         <v>1.0997</v>
@@ -688,13 +688,13 @@
         <v>3.3725</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0074</v>
+        <v>-0.0354</v>
       </c>
       <c r="T3" t="n">
         <v>-0.0452</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0379</v>
+        <v>0.0098</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3373</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1019</v>
+        <v>2.2881</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7363</v>
+        <v>0.8383</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3656</v>
+        <v>1.4498</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2494</v>
@@ -766,13 +766,13 @@
         <v>3.7693</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2953</v>
+        <v>-0.1091</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.544</v>
+        <v>-0.442</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2487</v>
+        <v>0.3329</v>
       </c>
       <c r="V4" t="n">
         <v>0.8692</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1418</v>
+        <v>0.228</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.7955</v>
+        <v>-2.2853</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6536</v>
+        <v>2.5133</v>
       </c>
       <c r="G5" t="n">
         <v>0.4416</v>
@@ -844,13 +844,13 @@
         <v>3.5709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5753</v>
+        <v>-0.2055</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1619</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5865</v>
+        <v>0.4463</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6032</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2366</v>
+        <v>0.0221</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8401</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6035</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0659</v>
@@ -922,13 +922,13 @@
         <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.7156</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.5611</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3509</v>
+        <v>-0.1545</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3866</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9431</v>
+        <v>-0.8807</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5277</v>
+        <v>-1.4654</v>
       </c>
       <c r="F7" t="n">
         <v>0.5847</v>
@@ -1000,10 +1000,10 @@
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4591</v>
+        <v>-0.3968</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5611</v>
+        <v>-0.4988</v>
       </c>
       <c r="U7" t="n">
         <v>0.102</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2098</v>
+        <v>-2.1577</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8962</v>
+        <v>-1.7318</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3136</v>
+        <v>-0.4258</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2532</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4943</v>
+        <v>-0.4421</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5611</v>
+        <v>-0.3967</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0668</v>
+        <v>-0.0454</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2558</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.201</v>
+        <v>-3.1729</v>
       </c>
       <c r="E9" t="n">
         <v>-3.2802</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1073</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2646</v>
@@ -1156,13 +1156,13 @@
         <v>2.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2817</v>
+        <v>-0.2536</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3683</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0867</v>
+        <v>0.1147</v>
       </c>
       <c r="V9" t="n">
         <v>-0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4168</v>
+        <v>-4.163</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0374</v>
+        <v>-5.5872</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6206</v>
+        <v>1.4242</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0324</v>
@@ -1234,13 +1234,13 @@
         <v>3.3725</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3395</v>
+        <v>-0.4067</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1248</v>
+        <v>-0.425</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2147</v>
+        <v>0.0183</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1206</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3286</v>
+        <v>1.640199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.5646</v>
+        <v>-9.252800000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>10.8931</v>
+        <v>10.8933</v>
       </c>
       <c r="G11" t="n">
         <v>-5.4819</v>
@@ -1312,10 +1312,10 @@
         <v>22.814</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.8624</v>
+        <v>-2.5506</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.9102</v>
+        <v>-3.5984</v>
       </c>
       <c r="U11" t="n">
         <v>1.0479</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4091</v>
+        <v>4.2784</v>
       </c>
       <c r="E12" t="n">
         <v>1.5114</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8977</v>
+        <v>2.767</v>
       </c>
       <c r="G12" t="n">
         <v>4.8428</v>
@@ -1390,13 +1390,13 @@
         <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2841</v>
+        <v>1.1534</v>
       </c>
       <c r="T12" t="n">
         <v>-0.255</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5391</v>
+        <v>1.4084</v>
       </c>
       <c r="V12" t="n">
         <v>0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5381</v>
+        <v>2.3868</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7756</v>
+        <v>2.9594</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2375</v>
+        <v>-0.5726</v>
       </c>
       <c r="G13" t="n">
         <v>1.005</v>
@@ -1468,13 +1468,13 @@
         <v>2.3806</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8741</v>
+        <v>0.7227</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0544</v>
+        <v>0.2382</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1803</v>
+        <v>0.4845</v>
       </c>
       <c r="V13" t="n">
         <v>0.4607</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7768</v>
+        <v>1.1601</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.569</v>
+        <v>-0.2167</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3458</v>
+        <v>1.3767</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5283</v>
+        <v>1.1662</v>
       </c>
       <c r="H14" t="n">
-        <v>1.829</v>
+        <v>1.0728</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3007</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2517</v>
+        <v>2.7877</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0686</v>
+        <v>2.1828</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3202</v>
+        <v>0.605</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7799</v>
+        <v>-1.6216</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7604</v>
+        <v>-1.1099</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0195</v>
+        <v>-0.5117</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1903</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1984</v>
+        <v>-2.9758</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2647</v>
+        <v>0.5215</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1189</v>
+        <v>-0.2946</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3837</v>
+        <v>0.8161</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0405</v>
+        <v>0.8253</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0329</v>
+        <v>-0.773</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.5983</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1662</v>
+        <v>0.5283</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0728</v>
+        <v>1.829</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09329999999999999</v>
+        <v>-1.3007</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7877</v>
+        <v>-0.2517</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1828</v>
+        <v>1.0686</v>
       </c>
       <c r="L15" t="n">
-        <v>0.605</v>
+        <v>-1.3202</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6216</v>
+        <v>0.7799</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1099</v>
+        <v>0.7604</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5117</v>
+        <v>0.0195</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9758</v>
+        <v>-0.1984</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6791</v>
+        <v>0.3132</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1109</v>
+        <v>-0.323</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4318</v>
+        <v>0.6362</v>
       </c>
       <c r="V15" t="n">
-        <v>0.266</v>
+        <v>-1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2092</v>
+        <v>-0.3036</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8808</v>
+        <v>-2.7787</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6716</v>
+        <v>2.4752</v>
       </c>
       <c r="G16" t="n">
         <v>0.5906</v>
@@ -1702,13 +1702,13 @@
         <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2714</v>
+        <v>0.1771</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4364</v>
+        <v>-0.3344</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7079</v>
+        <v>0.5115</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6745</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4174</v>
+        <v>-0.8791</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9316</v>
+        <v>-1.6458</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5142</v>
+        <v>0.7667</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0506</v>
@@ -1780,13 +1780,13 @@
         <v>0.5952</v>
       </c>
       <c r="S17" t="n">
-        <v>1.03</v>
+        <v>0.5683</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9977</v>
+        <v>0.2835</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0323</v>
+        <v>0.2848</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2268</v>
+        <v>-1.0714</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9938</v>
+        <v>-2.0827</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.233</v>
+        <v>1.0113</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4083</v>
+        <v>-0.3675</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4083</v>
+        <v>-0.3831</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0605</v>
+        <v>1.0064</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0605</v>
+        <v>1.0038</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4688</v>
+        <v>-1.3739</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4688</v>
+        <v>-1.3869</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0249</v>
+        <v>0.1374</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0623</v>
+        <v>-0.1133</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0374</v>
+        <v>0.2507</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7458</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1061</v>
+        <v>-1.1707</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5928</v>
+        <v>-0.9938</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4868</v>
+        <v>-0.1769</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3675</v>
+        <v>-0.4083</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3831</v>
+        <v>-0.4083</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0064</v>
+        <v>0.0605</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0038</v>
+        <v>0.0605</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0026</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3739</v>
+        <v>-0.4688</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3869</v>
+        <v>-0.4688</v>
       </c>
       <c r="O19" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5871</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8973</v>
+        <v>0.0312</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.0623</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2738</v>
+        <v>0.0935</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7458</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2543</v>
+        <v>-2.0043</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9109</v>
+        <v>-3.6048</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6566</v>
+        <v>1.6005</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4824</v>
@@ -2014,13 +2014,13 @@
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>0.212</v>
+        <v>0.462</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3004</v>
+        <v>0.0057</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5124</v>
+        <v>0.4562</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7984</v>
+        <v>-3.1897</v>
       </c>
       <c r="E21" t="n">
         <v>-3.2684</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.53</v>
+        <v>0.0788</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3419</v>
@@ -2092,13 +2092,13 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4727</v>
+        <v>0.136</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1926</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2801</v>
+        <v>0.3287</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6032</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3287</v>
+        <v>0.03180000000000094</v>
       </c>
       <c r="E22" t="n">
-        <v>-10.8932</v>
+        <v>-10.8931</v>
       </c>
       <c r="F22" t="n">
-        <v>9.5646</v>
+        <v>10.925</v>
       </c>
       <c r="G22" t="n">
         <v>5.4822</v>
@@ -2170,13 +2170,13 @@
         <v>13.8869</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8623</v>
+        <v>4.2228</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0479</v>
+        <v>-1.0478</v>
       </c>
       <c r="U22" t="n">
-        <v>3.9104</v>
+        <v>5.2706</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7456999999999998</v>
